--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_25_6.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_25_6.xlsx
@@ -513,661 +513,661 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_24</t>
+          <t>model_25_6_0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9991991178948684</v>
+        <v>0.9998934587054044</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7202998859218177</v>
+        <v>0.7055361105217944</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9952157613302549</v>
+        <v>0.9996371327055417</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9984439042854822</v>
+        <v>0.9998707294845435</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9972992424661569</v>
+        <v>0.9997712364439835</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0004754382139116567</v>
+        <v>6.324751481623581e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1660420701326158</v>
+        <v>0.1748064849719591</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001972777675377228</v>
+        <v>0.0001152567954365478</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0009885513389302208</v>
+        <v>1.221796298657727e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00148066458403677</v>
+        <v>6.373735080295239e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005713151024782608</v>
+        <v>0.003237355007141338</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02180454571669992</v>
+        <v>0.007952830616594056</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000565328544799</v>
+        <v>1.000075205619715</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02273281036949191</v>
+        <v>0.008291399080571372</v>
       </c>
       <c r="P2" t="n">
-        <v>131.302547247238</v>
+        <v>135.336909445143</v>
       </c>
       <c r="Q2" t="n">
-        <v>201.9973450895937</v>
+        <v>206.0317072874986</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_23</t>
+          <t>model_25_6_1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9992070008653607</v>
+        <v>0.9999098978767353</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7202327353610425</v>
+        <v>0.7052824909036286</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9952537792797759</v>
+        <v>0.999674473281182</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9984690153462796</v>
+        <v>0.9998514396882477</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9973280919991498</v>
+        <v>0.9997892491750162</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0004707585421007831</v>
+        <v>5.348851257895755e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1660819336062451</v>
+        <v>0.1749570445330993</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001957100998844996</v>
+        <v>0.0001033963848848639</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0009725988672785213</v>
+        <v>1.40411321472205e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001464848102463184</v>
+        <v>5.87187028296964e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00570666372690765</v>
+        <v>0.003074587879156229</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02169697080471795</v>
+        <v>0.007313584113070523</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000559764095039</v>
+        <v>1.000063601498775</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02262065577079611</v>
+        <v>0.007624938529970155</v>
       </c>
       <c r="P3" t="n">
-        <v>131.3223304897301</v>
+        <v>135.6720872905358</v>
       </c>
       <c r="Q3" t="n">
-        <v>202.0171283320858</v>
+        <v>206.3668851328914</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_22</t>
+          <t>model_25_6_2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9992155889436883</v>
+        <v>0.9999218690318263</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7201578143931813</v>
+        <v>0.7050497692735167</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9952956050810516</v>
+        <v>0.9996917045053436</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9984966566207142</v>
+        <v>0.999826834658484</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9973598326674444</v>
+        <v>0.9997948982996409</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004656602878198916</v>
+        <v>4.638191778995137e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1661264099291848</v>
+        <v>0.1750951981457848</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00193985415714096</v>
+        <v>9.792326645105927e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.000955039009875761</v>
+        <v>1.636666896337616e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001447446583508361</v>
+        <v>5.7144762276415e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005699359717191338</v>
+        <v>0.002929857013381102</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02157916327895713</v>
+        <v>0.006810427137114924</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000553701922102</v>
+        <v>1.000055151271652</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02249783293476845</v>
+        <v>0.007100361119869597</v>
       </c>
       <c r="P4" t="n">
-        <v>131.3441083715603</v>
+        <v>135.9572017549774</v>
       </c>
       <c r="Q4" t="n">
-        <v>202.0389062139159</v>
+        <v>206.651999597333</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_21</t>
+          <t>model_25_6_3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9992249095579243</v>
+        <v>0.9999303206079744</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7200741502770336</v>
+        <v>0.7048370733914948</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9953414638940077</v>
+        <v>0.9996936550781962</v>
       </c>
       <c r="E5" t="n">
-        <v>0.998527041485509</v>
+        <v>0.9997986508884968</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9973946862824526</v>
+        <v>0.9997912294117928</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0004601271685798316</v>
+        <v>4.136469709940207e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1661760765626318</v>
+        <v>0.1752214636093366</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001920944305717517</v>
+        <v>9.730370999149179e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0009357362134629494</v>
+        <v>1.903044931041917e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001428338421179241</v>
+        <v>5.81669757613905e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005691178390411128</v>
+        <v>0.002800618398439455</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02145057501746355</v>
+        <v>0.006431539248065121</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000547122664995</v>
+        <v>1.000049185453195</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0223637704047687</v>
+        <v>0.00670534318897689</v>
       </c>
       <c r="P5" t="n">
-        <v>131.3680153065058</v>
+        <v>136.1861655359583</v>
       </c>
       <c r="Q5" t="n">
-        <v>202.0628131488615</v>
+        <v>206.8809633783139</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_20</t>
+          <t>model_25_6_4</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9992349876178572</v>
+        <v>0.9999360245737787</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7199807325761551</v>
+        <v>0.7046427244347417</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9953915814340754</v>
+        <v>0.9996841523410115</v>
       </c>
       <c r="E6" t="n">
-        <v>0.998560430825674</v>
+        <v>0.9997683619788291</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9974328754801577</v>
+        <v>0.9997806749666427</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0004541443968541342</v>
+        <v>3.79785765994935e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1662315333453077</v>
+        <v>0.1753368375455031</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001900278370964819</v>
+        <v>0.0001003220449379182</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009145247438739076</v>
+        <v>2.189319628652841e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001407401557419363</v>
+        <v>6.110762061222331e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005681922403351292</v>
+        <v>0.002684976745176212</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02131066392335382</v>
+        <v>0.006162676090749335</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000540008740336</v>
+        <v>1.000045159124392</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02221790300572682</v>
+        <v>0.006425033970430708</v>
       </c>
       <c r="P6" t="n">
-        <v>131.3941907114936</v>
+        <v>136.3569766618311</v>
       </c>
       <c r="Q6" t="n">
-        <v>202.0889885538493</v>
+        <v>207.0517745041868</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_19</t>
+          <t>model_25_6_5</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9992458432770959</v>
+        <v>0.9999396044996574</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7198761164002883</v>
+        <v>0.7044653755761409</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9954463349790491</v>
+        <v>0.9996663521630569</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9985969989260374</v>
+        <v>0.9997370166163545</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9974746499410362</v>
+        <v>0.9997652120908651</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0004477000085900491</v>
+        <v>3.585337795316045e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1662936380264858</v>
+        <v>0.1754421194890403</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001877700782631897</v>
+        <v>0.0001059758789995223</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008912938820194094</v>
+        <v>2.485579357457719e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001384499107286409</v>
+        <v>6.541583628704975e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005671585017942522</v>
+        <v>0.002581520173808535</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02115892267082729</v>
+        <v>0.005987769029710519</v>
       </c>
       <c r="N7" t="n">
-        <v>1.00053234592205</v>
+        <v>1.000042632117889</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02205970181393254</v>
+        <v>0.006242680753695939</v>
       </c>
       <c r="P7" t="n">
-        <v>131.4227743470606</v>
+        <v>136.4721455414453</v>
       </c>
       <c r="Q7" t="n">
-        <v>202.1175721894162</v>
+        <v>207.1669433838009</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_18</t>
+          <t>model_25_6_6</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9992574836997821</v>
+        <v>0.9999415540365533</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7197592645097645</v>
+        <v>0.704303902168516</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9955059554960777</v>
+        <v>0.9996426929523893</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9986370397309972</v>
+        <v>0.9997053937207527</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9975202731882452</v>
+        <v>0.9997463630227788</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0004407897508434373</v>
+        <v>3.469604863614791e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1663630063564396</v>
+        <v>0.1755379770790944</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001853116301566557</v>
+        <v>0.0001134907056200086</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0008658568918744305</v>
+        <v>2.784462182073295e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001359486596720493</v>
+        <v>7.066750174393712e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005659996510766588</v>
+        <v>0.002488863495286649</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02099499347090723</v>
+        <v>0.005890335188777283</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000524129153095</v>
+        <v>1.000041255974198</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02188879380859166</v>
+        <v>0.00614109895243832</v>
       </c>
       <c r="P8" t="n">
-        <v>131.453885103317</v>
+        <v>136.537769499305</v>
       </c>
       <c r="Q8" t="n">
-        <v>202.1486829456726</v>
+        <v>207.2325673416606</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_17</t>
+          <t>model_25_6_7</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9992699130495195</v>
+        <v>0.9999422690837712</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7196282974592938</v>
+        <v>0.7041565580729372</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9955708391065456</v>
+        <v>0.9996151494712824</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9986807875892871</v>
+        <v>0.9996741374715804</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9975700168599289</v>
+        <v>0.9997253636306951</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0004334111519193475</v>
+        <v>3.427156571919086e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.166440754055081</v>
+        <v>0.1756254468991635</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001826361587375863</v>
+        <v>0.0001222392851035787</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0008380648971504495</v>
+        <v>3.079879659243269e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00133221510269742</v>
+        <v>7.651828341209199e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.005646740382325662</v>
+        <v>0.00240583916032353</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02081852905272963</v>
+        <v>0.005854192149151825</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000515355494457</v>
+        <v>1.000040751234985</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02170481693480053</v>
+        <v>0.0061034172287896</v>
       </c>
       <c r="P9" t="n">
-        <v>131.4876474759064</v>
+        <v>136.5623890707429</v>
       </c>
       <c r="Q9" t="n">
-        <v>202.1824453182621</v>
+        <v>207.2571869130985</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_16</t>
+          <t>model_25_6_8</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9992830789270755</v>
+        <v>0.9999420666034188</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7194816248159672</v>
+        <v>0.7040227255923381</v>
       </c>
       <c r="D10" t="n">
-        <v>0.995641053678764</v>
+        <v>0.999585222811883</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9987284891561156</v>
+        <v>0.9996437226985877</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9976240662101954</v>
+        <v>0.9997031422937923</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0004255953182657843</v>
+        <v>3.439176680305184e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.166527825272088</v>
+        <v>0.1757048956409093</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001797408654606339</v>
+        <v>0.000131744828626429</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0008077612035425942</v>
+        <v>3.367343950197239e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001302583061417536</v>
+        <v>8.270951933335336e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.00563181976943214</v>
+        <v>0.002331355366343868</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02062996166418601</v>
+        <v>0.005864449403230609</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000506061933829</v>
+        <v>1.000040894162293</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0215082218421383</v>
+        <v>0.00611411115540996</v>
       </c>
       <c r="P10" t="n">
-        <v>131.5240432406254</v>
+        <v>136.5553867187024</v>
       </c>
       <c r="Q10" t="n">
-        <v>202.218841082981</v>
+        <v>207.250184561058</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_15</t>
+          <t>model_25_6_9</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9992969065046176</v>
+        <v>0.9999411948352908</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7193172838984507</v>
+        <v>0.7039009367428661</v>
       </c>
       <c r="D11" t="n">
-        <v>0.995716799840649</v>
+        <v>0.9995541018813072</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9987803073241729</v>
+        <v>0.9996144613445619</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9976825709134272</v>
+        <v>0.9996804404381524</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0004173866709165952</v>
+        <v>3.490928602227898e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1666253851398837</v>
+        <v>0.1757771947629602</v>
       </c>
       <c r="I11" t="n">
-        <v>0.001766174774468399</v>
+        <v>0.0001416297060566637</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0007748423291211213</v>
+        <v>3.643906737281477e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.001270508415326831</v>
+        <v>8.903463580728147e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>0.005614996189127535</v>
+        <v>0.002264719355874979</v>
       </c>
       <c r="M11" t="n">
-        <v>0.02043004334103565</v>
+        <v>0.005908408078516495</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000496301290858</v>
+        <v>1.00004150952803</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02129979258208346</v>
+        <v>0.00615994124250977</v>
       </c>
       <c r="P11" t="n">
-        <v>131.5629949948562</v>
+        <v>136.5255153780213</v>
       </c>
       <c r="Q11" t="n">
-        <v>202.2577928372118</v>
+        <v>207.220313220377</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_14</t>
+          <t>model_25_6_10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9993112834647134</v>
+        <v>0.9999398462625936</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7191327579189689</v>
+        <v>0.7037904480964294</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9957981108543755</v>
+        <v>0.9995226291683548</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9988364757533909</v>
+        <v>0.999586609740725</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9977456882843837</v>
+        <v>0.9996577800793152</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0004088518863513539</v>
+        <v>3.570985703057247e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1667349277324114</v>
+        <v>0.1758427855963461</v>
       </c>
       <c r="I12" t="n">
-        <v>0.001732646231325991</v>
+        <v>0.0001516263194026453</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0007391598351774186</v>
+        <v>3.907145313839628e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>0.001235904918107322</v>
+        <v>9.534819057832966e-05</v>
       </c>
       <c r="L12" t="n">
-        <v>0.005596000137745956</v>
+        <v>0.002204919716839859</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02022008621028491</v>
+        <v>0.005975772504921224</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000486152848438</v>
+        <v>1.000042461461699</v>
       </c>
       <c r="O12" t="n">
-        <v>0.02108089714160548</v>
+        <v>0.006230173512010134</v>
       </c>
       <c r="P12" t="n">
-        <v>131.6043152071377</v>
+        <v>136.4801675999807</v>
       </c>
       <c r="Q12" t="n">
-        <v>202.2991130494933</v>
+        <v>207.1749654423363</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_13</t>
+          <t>model_25_6_11</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9993260446576425</v>
+        <v>0.9999381790207895</v>
       </c>
       <c r="C13" t="n">
-        <v>0.718925258417582</v>
+        <v>0.7036901078363217</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9958849374217398</v>
+        <v>0.9994915390792822</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9988971456805951</v>
+        <v>0.9995603047053541</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9978134916044382</v>
+        <v>0.9996355924630242</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0004000890045782768</v>
+        <v>3.669960378656773e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1668581083999463</v>
+        <v>0.1759023519092196</v>
       </c>
       <c r="I13" t="n">
-        <v>0.001696843353261191</v>
+        <v>0.0001615014007093785</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0007006176444812379</v>
+        <v>4.155766546134415e-05</v>
       </c>
       <c r="K13" t="n">
-        <v>0.001198732393944437</v>
+        <v>0.000101530031373458</v>
       </c>
       <c r="L13" t="n">
-        <v>0.005574248352498484</v>
+        <v>0.002151217734834568</v>
       </c>
       <c r="M13" t="n">
-        <v>0.02000222499069233</v>
+        <v>0.006058019790869598</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000475733182841</v>
+        <v>1.000043638338266</v>
       </c>
       <c r="O13" t="n">
-        <v>0.02085376111885994</v>
+        <v>0.006315922235196684</v>
       </c>
       <c r="P13" t="n">
-        <v>131.6476470483252</v>
+        <v>136.4254891979367</v>
       </c>
       <c r="Q13" t="n">
-        <v>202.3424448906808</v>
+        <v>207.1202870402923</v>
       </c>
     </row>
     <row r="14">
@@ -1177,712 +1177,712 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9993409365318376</v>
+        <v>0.999936308158655</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7186919023753429</v>
+        <v>0.7035991849025005</v>
       </c>
       <c r="D14" t="n">
-        <v>0.995977000568557</v>
+        <v>0.9994612761076679</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9989624021491009</v>
+        <v>0.9995356548861014</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9978859215625031</v>
+        <v>0.9996141631328982</v>
       </c>
       <c r="G14" t="n">
-        <v>0.000391248544760558</v>
+        <v>3.781022836666247e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1669966386270756</v>
+        <v>0.175956327690402</v>
       </c>
       <c r="I14" t="n">
-        <v>0.001658881175095931</v>
+        <v>0.0001711137663921782</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0006591617309962987</v>
+        <v>4.388743554225608e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>0.001159023359576839</v>
+        <v>0.0001075006009672171</v>
       </c>
       <c r="L14" t="n">
-        <v>0.005549553438524433</v>
+        <v>0.002102992346250148</v>
       </c>
       <c r="M14" t="n">
-        <v>0.01978000365926554</v>
+        <v>0.006149002225293342</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000465221271644</v>
+        <v>1.000044958946832</v>
       </c>
       <c r="O14" t="n">
-        <v>0.02062207936529274</v>
+        <v>0.00641077798021345</v>
       </c>
       <c r="P14" t="n">
-        <v>131.6923350711573</v>
+        <v>136.3658618004628</v>
       </c>
       <c r="Q14" t="n">
-        <v>202.3871329135129</v>
+        <v>207.0606596428185</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_11</t>
+          <t>model_25_6_13</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9993556124357689</v>
+        <v>0.9999343201300369</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7184290381371005</v>
+        <v>0.7035168260610187</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9960738571199926</v>
+        <v>0.999432161808368</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9990322094518386</v>
+        <v>0.9995125839392225</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9979627908073206</v>
+        <v>0.9995936536783425</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0003825362942209592</v>
+        <v>3.899040803276092e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1671526861940402</v>
+        <v>0.1760052194564223</v>
       </c>
       <c r="I15" t="n">
-        <v>0.001618942439682343</v>
+        <v>0.0001803612816406573</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0006148147785919064</v>
+        <v>4.606797898665737e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>0.001116880528546436</v>
+        <v>0.0001132148778500945</v>
       </c>
       <c r="L15" t="n">
-        <v>0.005521355506724605</v>
+        <v>0.002059639230976697</v>
       </c>
       <c r="M15" t="n">
-        <v>0.01955853507349053</v>
+        <v>0.006244229979169643</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000454861810046</v>
+        <v>1.00004636226115</v>
       </c>
       <c r="O15" t="n">
-        <v>0.02039118240331812</v>
+        <v>0.006510059776720892</v>
       </c>
       <c r="P15" t="n">
-        <v>131.737374044694</v>
+        <v>136.3043897799254</v>
       </c>
       <c r="Q15" t="n">
-        <v>202.4321718870496</v>
+        <v>206.999187622281</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_10</t>
+          <t>model_25_6_14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9993695903627132</v>
+        <v>0.9999322867594835</v>
       </c>
       <c r="C16" t="n">
-        <v>0.718132456536376</v>
+        <v>0.7034421808916993</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9961745264136654</v>
+        <v>0.9994044575876101</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9991064758393114</v>
+        <v>0.9994911647199561</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9980436773869963</v>
+        <v>0.999574230831581</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0003742383929717911</v>
+        <v>4.019750463028074e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1673287498438883</v>
+        <v>0.1760495320534338</v>
       </c>
       <c r="I16" t="n">
-        <v>0.001577431522509751</v>
+        <v>0.0001891609165302901</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0005676350735847433</v>
+        <v>4.809240990405067e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001072535231958736</v>
+        <v>0.0001186264076373894</v>
       </c>
       <c r="L16" t="n">
-        <v>0.005489105687690275</v>
+        <v>0.002020709151479295</v>
       </c>
       <c r="M16" t="n">
-        <v>0.01934524212750492</v>
+        <v>0.006340150205656073</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000444995038085</v>
+        <v>1.000047797581541</v>
       </c>
       <c r="O16" t="n">
-        <v>0.02016880913504463</v>
+        <v>0.006610063525831091</v>
       </c>
       <c r="P16" t="n">
-        <v>131.7812350984978</v>
+        <v>136.2434112762791</v>
       </c>
       <c r="Q16" t="n">
-        <v>202.4760329408535</v>
+        <v>206.9382091186348</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_9</t>
+          <t>model_25_6_15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9993822306705828</v>
+        <v>0.9999302573150004</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7177973869007002</v>
+        <v>0.7033746348005425</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9962776855817173</v>
+        <v>0.9993782952512852</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9991848731076721</v>
+        <v>0.9994712896789569</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9981278936613377</v>
+        <v>0.9995559470073598</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0003667345601875102</v>
+        <v>4.140227054288189e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1675276616538801</v>
+        <v>0.1760896303309837</v>
       </c>
       <c r="I17" t="n">
-        <v>0.001534893907271204</v>
+        <v>0.0001974708058258882</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0005178311162295451</v>
+        <v>4.997089328773406e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>0.00102636446199724</v>
+        <v>0.0001237205867046253</v>
       </c>
       <c r="L17" t="n">
-        <v>0.00545215147810625</v>
+        <v>0.001985767733893016</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01915031488481352</v>
+        <v>0.006434459615451938</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000436072467824</v>
+        <v>1.000049230130588</v>
       </c>
       <c r="O17" t="n">
-        <v>0.01996558343607684</v>
+        <v>0.006708387882449356</v>
       </c>
       <c r="P17" t="n">
-        <v>131.8217444816779</v>
+        <v>136.1843496692118</v>
       </c>
       <c r="Q17" t="n">
-        <v>202.5165423240335</v>
+        <v>206.8791475115675</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_8</t>
+          <t>model_25_6_16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9993926869840613</v>
+        <v>0.9999282673868004</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7174184075557373</v>
+        <v>0.7033134252238562</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9963814696670122</v>
+        <v>0.9993537373480553</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9992669074775594</v>
+        <v>0.9994529499772384</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9982144557887686</v>
+        <v>0.9995388371698908</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0003605272408175498</v>
+        <v>4.258357788281898e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1677526401641053</v>
+        <v>0.1761259669798207</v>
       </c>
       <c r="I18" t="n">
-        <v>0.001492098607817577</v>
+        <v>0.0002052710823240545</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0004657165930457983</v>
+        <v>5.170426455178692e-05</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0009789076004316877</v>
+        <v>0.0001284876734379207</v>
       </c>
       <c r="L18" t="n">
-        <v>0.005409703697952274</v>
+        <v>0.00195445097908827</v>
       </c>
       <c r="M18" t="n">
-        <v>0.01898755489307535</v>
+        <v>0.006525609387851757</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000428691540663</v>
+        <v>1.000050634785788</v>
       </c>
       <c r="O18" t="n">
-        <v>0.01979589441453075</v>
+        <v>0.006803418089366277</v>
       </c>
       <c r="P18" t="n">
-        <v>131.8558860802129</v>
+        <v>136.12808374944</v>
       </c>
       <c r="Q18" t="n">
-        <v>202.5506839225685</v>
+        <v>206.8228815917956</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_7</t>
+          <t>model_25_6_17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9993998245706713</v>
+        <v>0.9999263453502351</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7169891755493123</v>
+        <v>0.7032581981342426</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9964830087802913</v>
+        <v>0.9993308197568751</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9993516856058766</v>
+        <v>0.9994360711705389</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9983017597736432</v>
+        <v>0.9995229152526512</v>
       </c>
       <c r="G19" t="n">
-        <v>0.000356290061078056</v>
+        <v>4.3724581815695e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1680074508249764</v>
+        <v>0.1761587521659014</v>
       </c>
       <c r="I19" t="n">
-        <v>0.001450229021101248</v>
+        <v>0.0002125503498659363</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0004118590240813352</v>
+        <v>5.329955977269079e-05</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0009310440225912914</v>
+        <v>0.0001329237857375548</v>
       </c>
       <c r="L19" t="n">
-        <v>0.005360709418609289</v>
+        <v>0.001926270258459802</v>
       </c>
       <c r="M19" t="n">
-        <v>0.01887564730222665</v>
+        <v>0.006612456564371141</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000423653244232</v>
+        <v>1.000051991517481</v>
       </c>
       <c r="O19" t="n">
-        <v>0.01967922268585896</v>
+        <v>0.006893962529988531</v>
       </c>
       <c r="P19" t="n">
-        <v>131.8795307611095</v>
+        <v>136.0752002021377</v>
       </c>
       <c r="Q19" t="n">
-        <v>202.5743286034651</v>
+        <v>206.7699980444933</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_6</t>
+          <t>model_25_6_18</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9994022009548705</v>
+        <v>0.9999245112233496</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7165017184256968</v>
+        <v>0.7032082323613349</v>
       </c>
       <c r="D20" t="n">
-        <v>0.99657851210891</v>
+        <v>0.9993095344664993</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9994380720671384</v>
+        <v>0.9994206576458796</v>
       </c>
       <c r="F20" t="n">
-        <v>0.998387725736714</v>
+        <v>0.9995081637838039</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0003548793367629963</v>
+        <v>4.481339876504571e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1682968264306059</v>
+        <v>0.1761884140071084</v>
       </c>
       <c r="I20" t="n">
-        <v>0.001410848286228071</v>
+        <v>0.0002193111530469494</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0003569797186831977</v>
+        <v>5.475636431250167e-05</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0008839140024556343</v>
+        <v>0.000137033791549449</v>
       </c>
       <c r="L20" t="n">
-        <v>0.005304031928623287</v>
+        <v>0.001900782103363698</v>
       </c>
       <c r="M20" t="n">
-        <v>0.01883824133944027</v>
+        <v>0.006694281049152755</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000421975796562</v>
+        <v>1.000053286195283</v>
       </c>
       <c r="O20" t="n">
-        <v>0.01964022427379575</v>
+        <v>0.006979270452487332</v>
       </c>
       <c r="P20" t="n">
-        <v>131.887465445418</v>
+        <v>136.0260067673636</v>
       </c>
       <c r="Q20" t="n">
-        <v>202.5822632877737</v>
+        <v>206.7208046097192</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_5</t>
+          <t>model_25_6_19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9993979012662487</v>
+        <v>0.9999227718636856</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7159468560517219</v>
+        <v>0.7031631322588516</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9966626785065091</v>
+        <v>0.9992898292328765</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9995243564337538</v>
+        <v>0.9994065155648781</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9984693728320596</v>
+        <v>0.9994945350977147</v>
       </c>
       <c r="G21" t="n">
-        <v>0.000357431817665801</v>
+        <v>4.584595779797927e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1686262167046038</v>
+        <v>0.1762151873761655</v>
       </c>
       <c r="I21" t="n">
-        <v>0.001376142327419922</v>
+        <v>0.0002255700860380747</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0003021652716343051</v>
+        <v>5.609299874626069e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>0.000839151760398457</v>
+        <v>0.0001408309713160896</v>
       </c>
       <c r="L21" t="n">
-        <v>0.005238221552726179</v>
+        <v>0.001877977387183634</v>
       </c>
       <c r="M21" t="n">
-        <v>0.01890586728150288</v>
+        <v>0.00677096431817354</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000425010870883</v>
+        <v>1.000054513978575</v>
       </c>
       <c r="O21" t="n">
-        <v>0.01971072919221697</v>
+        <v>0.007059218287026582</v>
       </c>
       <c r="P21" t="n">
-        <v>131.873131867671</v>
+        <v>135.9804470491763</v>
       </c>
       <c r="Q21" t="n">
-        <v>202.5679297100266</v>
+        <v>206.675244891532</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_4</t>
+          <t>model_25_6_20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9993844420874998</v>
+        <v>0.9999211387927219</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7153146513402141</v>
+        <v>0.7031223841102034</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9967282293917551</v>
+        <v>0.9992716826344026</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9996080702115107</v>
+        <v>0.9993935826946567</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9985425224828656</v>
+        <v>0.9994819979221609</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0003654217675774067</v>
+        <v>4.68154192670281e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1690015207311765</v>
+        <v>0.1762393772374314</v>
       </c>
       <c r="I22" t="n">
-        <v>0.001349112462912496</v>
+        <v>0.0002313339529396213</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0002489838597735695</v>
+        <v>5.731534499526334e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0007990481613430326</v>
+        <v>0.0001443240380014786</v>
       </c>
       <c r="L22" t="n">
-        <v>0.005161783394456342</v>
+        <v>0.001857485797074422</v>
       </c>
       <c r="M22" t="n">
-        <v>0.01911600814964795</v>
+        <v>0.006842179423767554</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000434511467647</v>
+        <v>1.000055666734549</v>
       </c>
       <c r="O22" t="n">
-        <v>0.01992981619217054</v>
+        <v>0.007133465167101325</v>
       </c>
       <c r="P22" t="n">
-        <v>131.8289166877613</v>
+        <v>135.9385958755736</v>
       </c>
       <c r="Q22" t="n">
-        <v>202.5237145301169</v>
+        <v>206.6333937179292</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_3</t>
+          <t>model_25_6_21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9993586518887083</v>
+        <v>0.9999196123394442</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7145918697709616</v>
+        <v>0.7030855842446863</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9967655290558624</v>
+        <v>0.9992549934452688</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9996860399694081</v>
+        <v>0.9993818048845693</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9986017236010389</v>
+        <v>0.9994704840067148</v>
       </c>
       <c r="G23" t="n">
-        <v>0.00038073194365858</v>
+        <v>4.772158787208591e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1694305950932228</v>
+        <v>0.1762612232272738</v>
       </c>
       <c r="I23" t="n">
-        <v>0.001333731970899182</v>
+        <v>0.0002366349058977904</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0001994514898515533</v>
+        <v>5.842852109116584e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0007665917123963144</v>
+        <v>0.0001475320073156691</v>
       </c>
       <c r="L23" t="n">
-        <v>0.005072125452044154</v>
+        <v>0.001839009081929075</v>
       </c>
       <c r="M23" t="n">
-        <v>0.01951235361658301</v>
+        <v>0.006908081345213439</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000452716313853</v>
+        <v>1.000056744230981</v>
       </c>
       <c r="O23" t="n">
-        <v>0.02034303490618125</v>
+        <v>0.007202172669778945</v>
       </c>
       <c r="P23" t="n">
-        <v>131.7468299808065</v>
+        <v>135.9002533730337</v>
       </c>
       <c r="Q23" t="n">
-        <v>202.4416278231622</v>
+        <v>206.5950512153894</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_2</t>
+          <t>model_25_6_22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9993163617018959</v>
+        <v>0.9999181917943175</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7137629965086835</v>
+        <v>0.7030524619663716</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9967610737566488</v>
+        <v>0.9992396818352766</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9997539038491003</v>
+        <v>0.9993710749144734</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9986393668748904</v>
+        <v>0.9994599352194691</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0004058372253913909</v>
+        <v>4.856488482362475e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1699226500671717</v>
+        <v>0.1762808860424893</v>
       </c>
       <c r="I24" t="n">
-        <v>0.001335569110605695</v>
+        <v>0.0002414983012151302</v>
       </c>
       <c r="J24" t="n">
-        <v>0.000156339148811819</v>
+        <v>5.944266091273098e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0007459541461873344</v>
+        <v>0.0001504710757797655</v>
       </c>
       <c r="L24" t="n">
-        <v>0.00496744464902418</v>
+        <v>0.001822387624343939</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0201454020905861</v>
+        <v>0.006968851040424436</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000482568210426</v>
+        <v>1.000057746968717</v>
       </c>
       <c r="O24" t="n">
-        <v>0.02100303356431365</v>
+        <v>0.007265529456725686</v>
       </c>
       <c r="P24" t="n">
-        <v>131.6191168028697</v>
+        <v>135.86521964541</v>
       </c>
       <c r="Q24" t="n">
-        <v>202.3139146452253</v>
+        <v>206.5600174877656</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_0</t>
+          <t>model_25_6_23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9992546008794934</v>
+        <v>0.9999168751146998</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7129380297398531</v>
+        <v>0.7030225004569624</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9967228703014203</v>
+        <v>0.9992256738548988</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9998024938323481</v>
+        <v>0.999361254639533</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9986531518359538</v>
+        <v>0.9994502847623787</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0004425011174981251</v>
+        <v>4.934652272224644e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1704123859778582</v>
+        <v>0.1762986724887444</v>
       </c>
       <c r="I25" t="n">
-        <v>0.001351322280294667</v>
+        <v>0.0002459476273283766</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0001254710649594096</v>
+        <v>6.037082117663252e-05</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0007383966726329129</v>
+        <v>0.0001531598544457548</v>
       </c>
       <c r="L25" t="n">
-        <v>0.004858959423168995</v>
+        <v>0.001807490693002277</v>
       </c>
       <c r="M25" t="n">
-        <v>0.02103571052990902</v>
+        <v>0.007024708016867779</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000526164085064</v>
+        <v>1.000058676389624</v>
       </c>
       <c r="O25" t="n">
-        <v>0.02193124427709108</v>
+        <v>0.007323764380296103</v>
       </c>
       <c r="P25" t="n">
-        <v>131.4461351362</v>
+        <v>135.8332865122452</v>
       </c>
       <c r="Q25" t="n">
-        <v>202.1409329785556</v>
+        <v>206.5280843546008</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_1</t>
+          <t>model_25_6_24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.999254803902631</v>
+        <v>0.9999156584624195</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7129330471358901</v>
+        <v>0.7029954751365242</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9967232036310594</v>
+        <v>0.9992128489608312</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9998025568744726</v>
+        <v>0.9993523791341038</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9986533176800527</v>
+        <v>0.9994414713103832</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0004423805941935189</v>
+        <v>5.00687800725332e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1704153438668079</v>
+        <v>0.1763147158863896</v>
       </c>
       <c r="I26" t="n">
-        <v>0.001351184832036774</v>
+        <v>0.0002500211721603997</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0001254310157670241</v>
+        <v>6.120968684091959e-05</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0007383057501859294</v>
+        <v>0.0001556154295006596</v>
       </c>
       <c r="L26" t="n">
-        <v>0.004861597692028613</v>
+        <v>0.001794109899787209</v>
       </c>
       <c r="M26" t="n">
-        <v>0.02103284560380547</v>
+        <v>0.007075929626030293</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000526020774613</v>
+        <v>1.000059535202998</v>
       </c>
       <c r="O26" t="n">
-        <v>0.02192825738515209</v>
+        <v>0.007377166599404013</v>
       </c>
       <c r="P26" t="n">
-        <v>131.4466799471222</v>
+        <v>135.8042257927167</v>
       </c>
       <c r="Q26" t="n">
-        <v>202.1414777894778</v>
+        <v>206.4990236350723</v>
       </c>
     </row>
   </sheetData>
